--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.26004777963881</v>
+        <v>3.292257764191307</v>
       </c>
       <c r="D2" t="n">
-        <v>21.04709628740553</v>
+        <v>3.420153146703398</v>
       </c>
       <c r="E2" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F2" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.71919349588244</v>
+        <v>3.366868943080896</v>
       </c>
       <c r="D3" t="n">
-        <v>21.32916185800517</v>
+        <v>3.465988801925841</v>
       </c>
       <c r="E3" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F3" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.75355226951116</v>
+        <v>3.209952243795563</v>
       </c>
       <c r="D4" t="n">
-        <v>20.2626551680242</v>
+        <v>3.292681464803933</v>
       </c>
       <c r="E4" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F4" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.09142988207215</v>
+        <v>1.802357355836725</v>
       </c>
       <c r="D5" t="n">
-        <v>11.16198634725344</v>
+        <v>1.813822781428684</v>
       </c>
       <c r="E5" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F5" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.580989547940746</v>
+        <v>1.394410801540371</v>
       </c>
       <c r="D6" t="n">
-        <v>8.766217756075369</v>
+        <v>1.424510385362247</v>
       </c>
       <c r="E6" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F6" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.06672917854027</v>
+        <v>2.448343491512794</v>
       </c>
       <c r="D7" t="n">
-        <v>15.2082397410185</v>
+        <v>2.471338957915507</v>
       </c>
       <c r="E7" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F7" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.04893712373843</v>
+        <v>4.882952282607495</v>
       </c>
       <c r="D8" t="n">
-        <v>30.1351030128067</v>
+        <v>4.896954239581088</v>
       </c>
       <c r="E8" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F8" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.37825505067665</v>
+        <v>3.473966445734955</v>
       </c>
       <c r="D9" t="n">
-        <v>21.15495069493848</v>
+        <v>3.437679487927504</v>
       </c>
       <c r="E9" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F9" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>8.156986242604161</v>
+        <v>1.325510264423176</v>
       </c>
       <c r="D10" t="n">
-        <v>7.541789613854532</v>
+        <v>1.225540812251362</v>
       </c>
       <c r="E10" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F10" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.05126430469261</v>
+        <v>3.90833044951255</v>
       </c>
       <c r="D11" t="n">
-        <v>23.54226127159071</v>
+        <v>3.82561745663349</v>
       </c>
       <c r="E11" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F11" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.51680035628568</v>
+        <v>6.583980057896423</v>
       </c>
       <c r="D12" t="n">
-        <v>45.30783151324047</v>
+        <v>7.362522620901577</v>
       </c>
       <c r="E12" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F12" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.513178321383</v>
+        <v>6.583391477224738</v>
       </c>
       <c r="D13" t="n">
-        <v>39.87493126558864</v>
+        <v>6.479676330658154</v>
       </c>
       <c r="E13" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F13" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.73036966035612</v>
+        <v>3.53118506980787</v>
       </c>
       <c r="D14" t="n">
-        <v>21.00043364304064</v>
+        <v>3.412570466994105</v>
       </c>
       <c r="E14" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F14" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>51.61338928517333</v>
+        <v>8.387175758840666</v>
       </c>
       <c r="D15" t="n">
-        <v>52.48659644285107</v>
+        <v>8.529071921963299</v>
       </c>
       <c r="E15" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F15" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.64985054125534</v>
+        <v>7.580600712953993</v>
       </c>
       <c r="D16" t="n">
-        <v>47.49550845069551</v>
+        <v>7.718020123238021</v>
       </c>
       <c r="E16" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F16" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.09696012846898</v>
+        <v>7.165756020876209</v>
       </c>
       <c r="D17" t="n">
-        <v>43.52668305655239</v>
+        <v>7.073085996689764</v>
       </c>
       <c r="E17" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F17" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>24.6319507018863</v>
+        <v>4.002691989056524</v>
       </c>
       <c r="D18" t="n">
-        <v>25.42077780228722</v>
+        <v>4.130876392871674</v>
       </c>
       <c r="E18" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F18" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>15.16196244724726</v>
+        <v>2.46381889767768</v>
       </c>
       <c r="D19" t="n">
-        <v>10.23379812380679</v>
+        <v>1.662992195118603</v>
       </c>
       <c r="E19" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F19" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>8.010715547631778</v>
+        <v>1.301741276490164</v>
       </c>
       <c r="D20" t="n">
-        <v>11.98478351091654</v>
+        <v>1.947527320523938</v>
       </c>
       <c r="E20" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F20" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>64.83790197577409</v>
+        <v>10.53615907106329</v>
       </c>
       <c r="D21" t="n">
-        <v>64.28645021834313</v>
+        <v>10.44654816048076</v>
       </c>
       <c r="E21" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F21" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>56.91263357166842</v>
+        <v>9.248302955396118</v>
       </c>
       <c r="D22" t="n">
-        <v>56.34951687398798</v>
+        <v>9.156796492023046</v>
       </c>
       <c r="E22" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F22" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>23.24117625777519</v>
+        <v>3.776691141888469</v>
       </c>
       <c r="D23" t="n">
-        <v>22.52507959881027</v>
+        <v>3.660325434806669</v>
       </c>
       <c r="E23" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F23" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>26.09613887196243</v>
+        <v>4.240622566693895</v>
       </c>
       <c r="D24" t="n">
-        <v>26.21123864881746</v>
+        <v>4.259326280432838</v>
       </c>
       <c r="E24" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F24" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>52.9432662383721</v>
+        <v>8.603280763735466</v>
       </c>
       <c r="D25" t="n">
-        <v>52.24369154576621</v>
+        <v>8.489599876187009</v>
       </c>
       <c r="E25" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F25" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>36.91813499050755</v>
+        <v>5.999196935957477</v>
       </c>
       <c r="D26" t="n">
-        <v>36.10759001446122</v>
+        <v>5.867483377349948</v>
       </c>
       <c r="E26" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F26" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>35.5348064902283</v>
+        <v>5.774406054662099</v>
       </c>
       <c r="D27" t="n">
-        <v>35.41753386791759</v>
+        <v>5.755349253536608</v>
       </c>
       <c r="E27" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F27" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>27.65428701670588</v>
+        <v>4.493821640214705</v>
       </c>
       <c r="D28" t="n">
-        <v>26.76724253724933</v>
+        <v>4.349676912303017</v>
       </c>
       <c r="E28" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F28" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>14.43456641819192</v>
+        <v>2.345617042956187</v>
       </c>
       <c r="D29" t="n">
-        <v>15.08491401137612</v>
+        <v>2.45129852684862</v>
       </c>
       <c r="E29" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F29" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>69.94494476467101</v>
+        <v>11.36605352425904</v>
       </c>
       <c r="D30" t="n">
-        <v>69.19620252426898</v>
+        <v>11.24438291019371</v>
       </c>
       <c r="E30" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F30" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>41.3455709327971</v>
+        <v>6.718655276579528</v>
       </c>
       <c r="D31" t="n">
-        <v>41.04894069994752</v>
+        <v>6.670452863741472</v>
       </c>
       <c r="E31" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F31" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>50.9171488279994</v>
+        <v>8.274036684549902</v>
       </c>
       <c r="D32" t="n">
-        <v>50.08070534692478</v>
+        <v>8.138114618875278</v>
       </c>
       <c r="E32" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F32" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>43.43330873643917</v>
+        <v>7.057912669671365</v>
       </c>
       <c r="D33" t="n">
-        <v>42.58778717224995</v>
+        <v>6.920515415490618</v>
       </c>
       <c r="E33" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F33" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>32.83244293055343</v>
+        <v>5.335271976214932</v>
       </c>
       <c r="D34" t="n">
-        <v>32.9165802464285</v>
+        <v>5.34894429004463</v>
       </c>
       <c r="E34" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F34" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>22.91794177927895</v>
+        <v>3.724165539132829</v>
       </c>
       <c r="D35" t="n">
-        <v>24.34662924214799</v>
+        <v>3.956327251849049</v>
       </c>
       <c r="E35" t="n">
-        <v>16.31471317344532</v>
+        <v>2.651140890684865</v>
       </c>
       <c r="F35" t="n">
-        <v>16.23020273766375</v>
+        <v>2.637407944870359</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
